--- a/assets/formatos-notas/formato_1_y_2_bgu.xlsx
+++ b/assets/formatos-notas/formato_1_y_2_bgu.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A0A0E2-655B-4BFE-BE86-22C5E543D827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656BE99A-8E43-42D9-A342-884AF7A01A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="72">
   <si>
     <t>UNIDAD EDUCATIVA EMILIANO HINOSTROZA</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>EVALUACIÓN COMPORTAMENTAL</t>
   </si>
 </sst>
 </file>
@@ -689,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE18"/>
+  <dimension ref="A1:AS18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.21875" customWidth="1"/>
@@ -700,18 +703,20 @@
     <col min="13" max="13" width="49.88671875" customWidth="1"/>
     <col min="14" max="14" width="30" customWidth="1"/>
     <col min="15" max="15" width="48.109375" customWidth="1"/>
-    <col min="24" max="24" width="0" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="39.21875" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="33.21875" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="15.109375" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="29.44140625" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="0" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="15.109375" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="29.44140625" hidden="1" customWidth="1"/>
-    <col min="32" max="34" width="0" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="37" customWidth="1"/>
+    <col min="38" max="38" width="0" hidden="1" customWidth="1"/>
+    <col min="39" max="39" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="40" max="40" width="39.21875" hidden="1" customWidth="1"/>
+    <col min="41" max="41" width="33.21875" hidden="1" customWidth="1"/>
+    <col min="42" max="42" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="29.44140625" hidden="1" customWidth="1"/>
+    <col min="44" max="44" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="45" max="45" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="46" max="46" width="29.44140625" customWidth="1"/>
+    <col min="47" max="49" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="19.8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:44" ht="19.8" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -725,7 +730,7 @@
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>12</v>
       </c>
@@ -739,12 +744,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>23</v>
@@ -752,23 +757,23 @@
       <c r="D3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AN3" t="s">
         <v>58</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AO3" t="s">
         <v>26</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AP3" t="s">
         <v>27</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AQ3" t="s">
         <v>28</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AR3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
@@ -781,99 +786,99 @@
       <c r="D4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="AN4" t="s">
         <v>59</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AO4" t="s">
         <v>30</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AP4" t="s">
         <v>17</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AQ4" t="s">
         <v>16</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AR4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="AN5" t="s">
         <v>60</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AO5" t="s">
         <v>31</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AP5" t="s">
         <v>32</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AQ5" t="s">
         <v>33</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AR5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="AN6" t="s">
         <v>61</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AO6" t="s">
         <v>35</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AP6" t="s">
         <v>36</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AQ6" t="s">
         <v>37</v>
       </c>
-      <c r="AC6" t="s">
+      <c r="AR6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="AN7" t="s">
         <v>62</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AO7" t="s">
         <v>39</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="AP7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
-      <c r="Y8" t="s">
+      <c r="AN8" t="s">
         <v>63</v>
       </c>
-      <c r="Z8" t="s">
+      <c r="AO8" t="s">
         <v>41</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AP8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
@@ -919,17 +924,20 @@
       <c r="O9" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="Y9" t="s">
+      <c r="P9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AN9" t="s">
         <v>64</v>
       </c>
-      <c r="Z9" t="s">
+      <c r="AO9" t="s">
         <v>43</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AP9" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="4"/>
       <c r="C10" s="3"/>
@@ -945,14 +953,15 @@
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
-      <c r="Z10" t="s">
+      <c r="P10" s="3"/>
+      <c r="AO10" t="s">
         <v>45</v>
       </c>
-      <c r="AA10" t="s">
+      <c r="AP10" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="4"/>
       <c r="C11" s="3"/>
@@ -968,14 +977,15 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-      <c r="Z11" t="s">
+      <c r="P11" s="3"/>
+      <c r="AO11" t="s">
         <v>46</v>
       </c>
-      <c r="AA11" t="s">
+      <c r="AP11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="4"/>
       <c r="C12" s="3"/>
@@ -991,14 +1001,15 @@
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
-      <c r="Z12" t="s">
+      <c r="P12" s="3"/>
+      <c r="AO12" t="s">
         <v>47</v>
       </c>
-      <c r="AA12" t="s">
+      <c r="AP12" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="4"/>
       <c r="C13" s="3"/>
@@ -1014,14 +1025,15 @@
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
-      <c r="Z13" t="s">
+      <c r="P13" s="3"/>
+      <c r="AO13" t="s">
         <v>48</v>
       </c>
-      <c r="AA13" t="s">
+      <c r="AP13" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
       <c r="B14" s="4"/>
       <c r="C14" s="3"/>
@@ -1037,14 +1049,15 @@
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
-      <c r="Z14" t="s">
+      <c r="P14" s="3"/>
+      <c r="AO14" t="s">
         <v>49</v>
       </c>
-      <c r="AA14" t="s">
+      <c r="AP14" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="4"/>
       <c r="C15" s="3"/>
@@ -1060,11 +1073,12 @@
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
-      <c r="Z15" t="s">
+      <c r="P15" s="3"/>
+      <c r="AO15" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" s="7"/>
       <c r="B16" s="4"/>
       <c r="C16" s="3"/>
@@ -1080,17 +1094,18 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-      <c r="Z16" t="s">
+      <c r="P16" s="3"/>
+      <c r="AO16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="26:26" x14ac:dyDescent="0.3">
-      <c r="Z17" t="s">
+    <row r="17" spans="41:41" x14ac:dyDescent="0.3">
+      <c r="AO17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="26:26" x14ac:dyDescent="0.3">
-      <c r="Z18" t="s">
+    <row r="18" spans="41:41" x14ac:dyDescent="0.3">
+      <c r="AO18" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1100,19 +1115,19 @@
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{BA29F8F6-4357-424C-926B-ABF848246A12}">
-      <formula1>$Y$4:Y$9</formula1>
+      <formula1>$AN$4:AN$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{1111DBC0-3B92-4B3D-A296-AB24C7349FBB}">
-      <formula1>$Z$4:$Z$18</formula1>
+      <formula1>$AO$4:$AO$18</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4" xr:uid="{08909813-B489-4B84-A754-485066F9D523}">
-      <formula1>AB$4:AB$6</formula1>
+      <formula1>AQ$4:AQ$6</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{D0130D7C-E58C-49AD-B5F3-99115349199D}">
-      <formula1>$AA$4:$AA$14</formula1>
+      <formula1>$AP$4:$AP$14</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6" xr:uid="{D03738F8-5189-4E2B-948E-C83D3DB07424}">
-      <formula1>$AC$4:$AC$6</formula1>
+      <formula1>$AR$4:$AR$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/assets/formatos-notas/formato_1_y_2_bgu.xlsx
+++ b/assets/formatos-notas/formato_1_y_2_bgu.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656BE99A-8E43-42D9-A342-884AF7A01A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6BC4EEB-B6BE-4366-8114-1B9DDAE30C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -240,10 +240,10 @@
     <t>EMPRENDIMIENTO Y GESTIÓN</t>
   </si>
   <si>
-    <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
-  </si>
-  <si>
     <t>EVALUACIÓN COMPORTAMENTAL</t>
+  </si>
+  <si>
+    <t>CÍVICA Y ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
   </si>
 </sst>
 </file>
@@ -692,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AS18"/>
+  <dimension ref="A1:AS31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.21875" customWidth="1"/>
@@ -922,10 +922,10 @@
         <v>69</v>
       </c>
       <c r="O9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="P9" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="AN9" t="s">
         <v>64</v>
@@ -1099,15 +1099,281 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="41:41" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
       <c r="AO17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="41:41" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A18" s="7"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
       <c r="AO18" t="s">
         <v>14</v>
       </c>
+    </row>
+    <row r="19" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A21" s="7"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A22" s="7"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A23" s="7"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A24" s="7"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A25" s="7"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A26" s="7"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A27" s="7"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A28" s="7"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A29" s="7"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A30" s="7"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A31" s="7"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/assets/formatos-notas/formato_1_y_2_bgu.xlsx
+++ b/assets/formatos-notas/formato_1_y_2_bgu.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6BC4EEB-B6BE-4366-8114-1B9DDAE30C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9887E16F-D207-4C39-9A3E-BCC1FD53B4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="73">
   <si>
     <t>UNIDAD EDUCATIVA EMILIANO HINOSTROZA</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>CÍVICA Y ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>PARTICIPACIÓN ESTUDIANTIL</t>
   </si>
 </sst>
 </file>
@@ -692,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AS31"/>
+  <dimension ref="A1:AT31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.21875" customWidth="1"/>
@@ -701,22 +704,22 @@
     <col min="4" max="4" width="34.33203125" customWidth="1"/>
     <col min="5" max="12" width="30" customWidth="1"/>
     <col min="13" max="13" width="49.88671875" customWidth="1"/>
-    <col min="14" max="14" width="30" customWidth="1"/>
-    <col min="15" max="15" width="48.109375" customWidth="1"/>
-    <col min="16" max="16" width="37" customWidth="1"/>
-    <col min="38" max="38" width="0" hidden="1" customWidth="1"/>
-    <col min="39" max="39" width="9.109375" hidden="1" customWidth="1"/>
-    <col min="40" max="40" width="39.21875" hidden="1" customWidth="1"/>
-    <col min="41" max="41" width="33.21875" hidden="1" customWidth="1"/>
-    <col min="42" max="42" width="15.109375" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="29.44140625" hidden="1" customWidth="1"/>
-    <col min="44" max="44" width="9.109375" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="15.109375" hidden="1" customWidth="1"/>
-    <col min="46" max="46" width="29.44140625" customWidth="1"/>
-    <col min="47" max="49" width="9.109375" customWidth="1"/>
+    <col min="14" max="15" width="30" customWidth="1"/>
+    <col min="16" max="16" width="48.109375" customWidth="1"/>
+    <col min="17" max="17" width="37" customWidth="1"/>
+    <col min="39" max="39" width="0" hidden="1" customWidth="1"/>
+    <col min="40" max="40" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="41" max="41" width="39.21875" hidden="1" customWidth="1"/>
+    <col min="42" max="42" width="33.21875" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="44" max="44" width="29.44140625" hidden="1" customWidth="1"/>
+    <col min="45" max="45" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="46" max="46" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="47" max="47" width="29.44140625" customWidth="1"/>
+    <col min="48" max="50" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="19.8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:45" ht="19.8" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -730,7 +733,7 @@
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>12</v>
       </c>
@@ -744,7 +747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>13</v>
       </c>
@@ -757,23 +760,23 @@
       <c r="D3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AN3" t="s">
+      <c r="AO3" t="s">
         <v>58</v>
       </c>
-      <c r="AO3" t="s">
+      <c r="AP3" t="s">
         <v>26</v>
       </c>
-      <c r="AP3" t="s">
+      <c r="AQ3" t="s">
         <v>27</v>
       </c>
-      <c r="AQ3" t="s">
+      <c r="AR3" t="s">
         <v>28</v>
       </c>
-      <c r="AR3" t="s">
+      <c r="AS3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
@@ -786,99 +789,99 @@
       <c r="D4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AO4" t="s">
         <v>59</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AP4" t="s">
         <v>30</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AQ4" t="s">
         <v>17</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AR4" t="s">
         <v>16</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AS4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="AN5" t="s">
+      <c r="AO5" t="s">
         <v>60</v>
       </c>
-      <c r="AO5" t="s">
+      <c r="AP5" t="s">
         <v>31</v>
       </c>
-      <c r="AP5" t="s">
+      <c r="AQ5" t="s">
         <v>32</v>
       </c>
-      <c r="AQ5" t="s">
+      <c r="AR5" t="s">
         <v>33</v>
       </c>
-      <c r="AR5" t="s">
+      <c r="AS5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="AN6" t="s">
+      <c r="AO6" t="s">
         <v>61</v>
       </c>
-      <c r="AO6" t="s">
+      <c r="AP6" t="s">
         <v>35</v>
       </c>
-      <c r="AP6" t="s">
+      <c r="AQ6" t="s">
         <v>36</v>
       </c>
-      <c r="AQ6" t="s">
+      <c r="AR6" t="s">
         <v>37</v>
       </c>
-      <c r="AR6" t="s">
+      <c r="AS6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="AN7" t="s">
+      <c r="AO7" t="s">
         <v>62</v>
       </c>
-      <c r="AO7" t="s">
+      <c r="AP7" t="s">
         <v>39</v>
       </c>
-      <c r="AP7" t="s">
+      <c r="AQ7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
-      <c r="AN8" t="s">
+      <c r="AO8" t="s">
         <v>63</v>
       </c>
-      <c r="AO8" t="s">
+      <c r="AP8" t="s">
         <v>41</v>
       </c>
-      <c r="AP8" t="s">
+      <c r="AQ8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
@@ -922,22 +925,25 @@
         <v>69</v>
       </c>
       <c r="O9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P9" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="Q9" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AN9" t="s">
+      <c r="AO9" t="s">
         <v>64</v>
       </c>
-      <c r="AO9" t="s">
+      <c r="AP9" t="s">
         <v>43</v>
       </c>
-      <c r="AP9" t="s">
+      <c r="AQ9" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="4"/>
       <c r="C10" s="3"/>
@@ -954,14 +960,15 @@
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
-      <c r="AO10" t="s">
+      <c r="Q10" s="3"/>
+      <c r="AP10" t="s">
         <v>45</v>
       </c>
-      <c r="AP10" t="s">
+      <c r="AQ10" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="4"/>
       <c r="C11" s="3"/>
@@ -978,14 +985,15 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-      <c r="AO11" t="s">
+      <c r="Q11" s="3"/>
+      <c r="AP11" t="s">
         <v>46</v>
       </c>
-      <c r="AP11" t="s">
+      <c r="AQ11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="4"/>
       <c r="C12" s="3"/>
@@ -1002,14 +1010,15 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
-      <c r="AO12" t="s">
+      <c r="Q12" s="3"/>
+      <c r="AP12" t="s">
         <v>47</v>
       </c>
-      <c r="AP12" t="s">
+      <c r="AQ12" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="4"/>
       <c r="C13" s="3"/>
@@ -1026,14 +1035,15 @@
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
-      <c r="AO13" t="s">
+      <c r="Q13" s="3"/>
+      <c r="AP13" t="s">
         <v>48</v>
       </c>
-      <c r="AP13" t="s">
+      <c r="AQ13" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
       <c r="B14" s="4"/>
       <c r="C14" s="3"/>
@@ -1050,14 +1060,15 @@
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
-      <c r="AO14" t="s">
+      <c r="Q14" s="3"/>
+      <c r="AP14" t="s">
         <v>49</v>
       </c>
-      <c r="AP14" t="s">
+      <c r="AQ14" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="4"/>
       <c r="C15" s="3"/>
@@ -1074,11 +1085,12 @@
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
-      <c r="AO15" t="s">
+      <c r="Q15" s="3"/>
+      <c r="AP15" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.3">
       <c r="A16" s="7"/>
       <c r="B16" s="4"/>
       <c r="C16" s="3"/>
@@ -1095,11 +1107,12 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-      <c r="AO16" t="s">
+      <c r="Q16" s="3"/>
+      <c r="AP16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="B17" s="4"/>
       <c r="C17" s="3"/>
@@ -1116,11 +1129,12 @@
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
-      <c r="AO17" t="s">
+      <c r="Q17" s="3"/>
+      <c r="AP17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
       <c r="B18" s="4"/>
       <c r="C18" s="3"/>
@@ -1137,11 +1151,12 @@
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
-      <c r="AO18" t="s">
+      <c r="Q18" s="3"/>
+      <c r="AP18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A19" s="7"/>
       <c r="B19" s="4"/>
       <c r="C19" s="3"/>
@@ -1158,8 +1173,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="B20" s="4"/>
       <c r="C20" s="3"/>
@@ -1176,8 +1192,9 @@
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="B21" s="4"/>
       <c r="C21" s="3"/>
@@ -1194,8 +1211,9 @@
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A22" s="7"/>
       <c r="B22" s="4"/>
       <c r="C22" s="3"/>
@@ -1212,8 +1230,9 @@
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="4"/>
       <c r="C23" s="3"/>
@@ -1230,8 +1249,9 @@
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="4"/>
       <c r="C24" s="3"/>
@@ -1248,8 +1268,9 @@
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A25" s="7"/>
       <c r="B25" s="4"/>
       <c r="C25" s="3"/>
@@ -1266,8 +1287,9 @@
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A26" s="7"/>
       <c r="B26" s="4"/>
       <c r="C26" s="3"/>
@@ -1284,8 +1306,9 @@
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A27" s="7"/>
       <c r="B27" s="4"/>
       <c r="C27" s="3"/>
@@ -1302,8 +1325,9 @@
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A28" s="7"/>
       <c r="B28" s="4"/>
       <c r="C28" s="3"/>
@@ -1320,8 +1344,9 @@
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A29" s="7"/>
       <c r="B29" s="4"/>
       <c r="C29" s="3"/>
@@ -1338,8 +1363,9 @@
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A30" s="7"/>
       <c r="B30" s="4"/>
       <c r="C30" s="3"/>
@@ -1356,8 +1382,9 @@
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A31" s="7"/>
       <c r="B31" s="4"/>
       <c r="C31" s="3"/>
@@ -1374,6 +1401,7 @@
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1381,19 +1409,19 @@
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{BA29F8F6-4357-424C-926B-ABF848246A12}">
-      <formula1>$AN$4:AN$9</formula1>
+      <formula1>$AO$4:AO$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{1111DBC0-3B92-4B3D-A296-AB24C7349FBB}">
-      <formula1>$AO$4:$AO$18</formula1>
+      <formula1>$AP$4:$AP$18</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4" xr:uid="{08909813-B489-4B84-A754-485066F9D523}">
-      <formula1>AQ$4:AQ$6</formula1>
+      <formula1>AR$4:AR$6</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{D0130D7C-E58C-49AD-B5F3-99115349199D}">
-      <formula1>$AP$4:$AP$14</formula1>
+      <formula1>$AQ$4:$AQ$14</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6" xr:uid="{D03738F8-5189-4E2B-948E-C83D3DB07424}">
-      <formula1>$AR$4:$AR$6</formula1>
+      <formula1>$AS$4:$AS$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/assets/formatos-notas/formato_1_y_2_bgu.xlsx
+++ b/assets/formatos-notas/formato_1_y_2_bgu.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9887E16F-D207-4C39-9A3E-BCC1FD53B4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F350F21-C923-4970-91D5-541BC299EEA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="72">
   <si>
     <t>UNIDAD EDUCATIVA EMILIANO HINOSTROZA</t>
   </si>
@@ -244,9 +244,6 @@
   </si>
   <si>
     <t>CÍVICA Y ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
-  </si>
-  <si>
-    <t>PARTICIPACIÓN ESTUDIANTIL</t>
   </si>
 </sst>
 </file>
@@ -704,22 +701,22 @@
     <col min="4" max="4" width="34.33203125" customWidth="1"/>
     <col min="5" max="12" width="30" customWidth="1"/>
     <col min="13" max="13" width="49.88671875" customWidth="1"/>
-    <col min="14" max="15" width="30" customWidth="1"/>
-    <col min="16" max="16" width="48.109375" customWidth="1"/>
-    <col min="17" max="17" width="37" customWidth="1"/>
-    <col min="39" max="39" width="0" hidden="1" customWidth="1"/>
-    <col min="40" max="40" width="9.109375" hidden="1" customWidth="1"/>
-    <col min="41" max="41" width="39.21875" hidden="1" customWidth="1"/>
-    <col min="42" max="42" width="33.21875" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="15.109375" hidden="1" customWidth="1"/>
-    <col min="44" max="44" width="29.44140625" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="9.109375" hidden="1" customWidth="1"/>
-    <col min="46" max="46" width="15.109375" hidden="1" customWidth="1"/>
-    <col min="47" max="47" width="29.44140625" customWidth="1"/>
-    <col min="48" max="50" width="9.109375" customWidth="1"/>
+    <col min="14" max="14" width="30" customWidth="1"/>
+    <col min="15" max="15" width="48.109375" customWidth="1"/>
+    <col min="16" max="16" width="37" customWidth="1"/>
+    <col min="38" max="38" width="0" hidden="1" customWidth="1"/>
+    <col min="39" max="39" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="40" max="40" width="39.21875" hidden="1" customWidth="1"/>
+    <col min="41" max="41" width="33.21875" hidden="1" customWidth="1"/>
+    <col min="42" max="42" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="29.44140625" hidden="1" customWidth="1"/>
+    <col min="44" max="44" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="45" max="45" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="46" max="46" width="29.44140625" customWidth="1"/>
+    <col min="47" max="49" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="19.8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:44" ht="19.8" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -733,7 +730,7 @@
       <c r="I1" s="8"/>
       <c r="J1" s="8"/>
     </row>
-    <row r="2" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>12</v>
       </c>
@@ -747,7 +744,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>13</v>
       </c>
@@ -760,23 +757,23 @@
       <c r="D3" s="6" t="s">
         <v>24</v>
       </c>
+      <c r="AN3" t="s">
+        <v>58</v>
+      </c>
       <c r="AO3" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="AP3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AS3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
@@ -789,99 +786,99 @@
       <c r="D4" s="6" t="s">
         <v>24</v>
       </c>
+      <c r="AN4" t="s">
+        <v>59</v>
+      </c>
       <c r="AO4" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="AP4" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="AQ4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR4" t="s">
-        <v>16</v>
-      </c>
-      <c r="AS4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="AN5" t="s">
+        <v>60</v>
+      </c>
       <c r="AO5" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="AP5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AQ5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AR5" t="s">
-        <v>33</v>
-      </c>
-      <c r="AS5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>20</v>
       </c>
+      <c r="AN6" t="s">
+        <v>61</v>
+      </c>
       <c r="AO6" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="AP6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AQ6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AR6" t="s">
-        <v>37</v>
-      </c>
-      <c r="AS6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>22</v>
       </c>
+      <c r="AN7" t="s">
+        <v>62</v>
+      </c>
       <c r="AO7" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="AP7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AQ7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
+      <c r="AN8" t="s">
+        <v>63</v>
+      </c>
       <c r="AO8" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="AP8" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
@@ -925,25 +922,22 @@
         <v>69</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q9" s="2" t="s">
         <v>70</v>
       </c>
+      <c r="AN9" t="s">
+        <v>64</v>
+      </c>
       <c r="AO9" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="AP9" t="s">
-        <v>43</v>
-      </c>
-      <c r="AQ9" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="4"/>
       <c r="C10" s="3"/>
@@ -960,15 +954,14 @@
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
+      <c r="AO10" t="s">
+        <v>45</v>
+      </c>
       <c r="AP10" t="s">
-        <v>45</v>
-      </c>
-      <c r="AQ10" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="4"/>
       <c r="C11" s="3"/>
@@ -985,15 +978,14 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
+      <c r="AO11" t="s">
+        <v>46</v>
+      </c>
       <c r="AP11" t="s">
-        <v>46</v>
-      </c>
-      <c r="AQ11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="4"/>
       <c r="C12" s="3"/>
@@ -1010,15 +1002,14 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
+      <c r="AO12" t="s">
+        <v>47</v>
+      </c>
       <c r="AP12" t="s">
-        <v>47</v>
-      </c>
-      <c r="AQ12" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="4"/>
       <c r="C13" s="3"/>
@@ -1035,15 +1026,14 @@
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
+      <c r="AO13" t="s">
+        <v>48</v>
+      </c>
       <c r="AP13" t="s">
-        <v>48</v>
-      </c>
-      <c r="AQ13" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
       <c r="B14" s="4"/>
       <c r="C14" s="3"/>
@@ -1060,15 +1050,14 @@
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
+      <c r="AO14" t="s">
+        <v>49</v>
+      </c>
       <c r="AP14" t="s">
-        <v>49</v>
-      </c>
-      <c r="AQ14" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="4"/>
       <c r="C15" s="3"/>
@@ -1085,12 +1074,11 @@
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="AP15" t="s">
+      <c r="AO15" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" s="7"/>
       <c r="B16" s="4"/>
       <c r="C16" s="3"/>
@@ -1107,12 +1095,11 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="AP16" t="s">
+      <c r="AO16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="B17" s="4"/>
       <c r="C17" s="3"/>
@@ -1129,12 +1116,11 @@
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="AP17" t="s">
+      <c r="AO17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
       <c r="B18" s="4"/>
       <c r="C18" s="3"/>
@@ -1151,12 +1137,11 @@
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="AP18" t="s">
+      <c r="AO18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A19" s="7"/>
       <c r="B19" s="4"/>
       <c r="C19" s="3"/>
@@ -1173,9 +1158,8 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="B20" s="4"/>
       <c r="C20" s="3"/>
@@ -1192,9 +1176,8 @@
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="B21" s="4"/>
       <c r="C21" s="3"/>
@@ -1211,9 +1194,8 @@
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A22" s="7"/>
       <c r="B22" s="4"/>
       <c r="C22" s="3"/>
@@ -1230,9 +1212,8 @@
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="4"/>
       <c r="C23" s="3"/>
@@ -1249,9 +1230,8 @@
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="4"/>
       <c r="C24" s="3"/>
@@ -1268,9 +1248,8 @@
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A25" s="7"/>
       <c r="B25" s="4"/>
       <c r="C25" s="3"/>
@@ -1287,9 +1266,8 @@
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A26" s="7"/>
       <c r="B26" s="4"/>
       <c r="C26" s="3"/>
@@ -1306,9 +1284,8 @@
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A27" s="7"/>
       <c r="B27" s="4"/>
       <c r="C27" s="3"/>
@@ -1325,9 +1302,8 @@
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A28" s="7"/>
       <c r="B28" s="4"/>
       <c r="C28" s="3"/>
@@ -1344,9 +1320,8 @@
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A29" s="7"/>
       <c r="B29" s="4"/>
       <c r="C29" s="3"/>
@@ -1363,9 +1338,8 @@
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A30" s="7"/>
       <c r="B30" s="4"/>
       <c r="C30" s="3"/>
@@ -1382,9 +1356,8 @@
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A31" s="7"/>
       <c r="B31" s="4"/>
       <c r="C31" s="3"/>
@@ -1401,7 +1374,6 @@
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
-      <c r="Q31" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1409,19 +1381,19 @@
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{BA29F8F6-4357-424C-926B-ABF848246A12}">
-      <formula1>$AO$4:AO$9</formula1>
+      <formula1>$AN$4:AN$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{1111DBC0-3B92-4B3D-A296-AB24C7349FBB}">
-      <formula1>$AP$4:$AP$18</formula1>
+      <formula1>$AO$4:$AO$18</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4" xr:uid="{08909813-B489-4B84-A754-485066F9D523}">
-      <formula1>AR$4:AR$6</formula1>
+      <formula1>AQ$4:AQ$6</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{D0130D7C-E58C-49AD-B5F3-99115349199D}">
-      <formula1>$AQ$4:$AQ$14</formula1>
+      <formula1>$AP$4:$AP$14</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6" xr:uid="{D03738F8-5189-4E2B-948E-C83D3DB07424}">
-      <formula1>$AS$4:$AS$6</formula1>
+      <formula1>$AR$4:$AR$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
